--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -1,36 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_Plzeňský-KV" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES1" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SYSTEM" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="30_Plzeňský-KV" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="NOTES1" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SYSTEM" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,11 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10905,7 +10923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11482,6 +11500,23 @@
       <c r="D26" t="inlineStr">
         <is>
           <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0031</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K227"/>
+  <dimension ref="A1:L227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11635,6 +11670,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11672,6 +11712,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Playoff nehráno (COVID-19). Bez mistra.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11709,6 +11754,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11746,6 +11796,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11783,6 +11838,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11820,6 +11880,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11857,6 +11922,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11894,6 +11964,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11931,6 +12006,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11968,6 +12048,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12005,6 +12090,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12042,6 +12132,11 @@
           <t>1.liga: základ + QF/SF + Play out + baráž.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12079,6 +12174,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12116,6 +12216,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12153,6 +12258,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12190,6 +12300,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12227,6 +12342,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12264,6 +12384,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12301,6 +12426,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12338,6 +12468,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12375,6 +12510,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12412,6 +12552,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12449,6 +12594,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12486,6 +12636,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12523,6 +12678,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12560,6 +12720,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12597,6 +12762,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12634,6 +12804,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12671,6 +12846,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12708,6 +12888,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12745,6 +12930,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12777,6 +12967,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0033</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12814,6 +13009,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0034</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12883,6 +13083,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0039</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12920,6 +13125,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0040</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12952,6 +13162,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0049</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13026,6 +13241,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0051</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13063,6 +13283,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0052</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13803,6 +14028,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0066</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -13840,6 +14070,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0067</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -14316,6 +14551,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0076</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -15310,6 +15550,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0126</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -15416,6 +15661,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0089</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -16336,6 +16586,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0143</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -16664,6 +16919,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0153</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17066,6 +17326,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0169</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -17542,6 +17807,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0186</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -17653,6 +17923,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0191</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -18462,6 +18737,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0218</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -18938,6 +19218,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0229</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -19486,6 +19771,11 @@
       <c r="J215" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0242</t>
         </is>
       </c>
     </row>
@@ -35204,6 +35494,81 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -11611,7 +11611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L227"/>
+  <dimension ref="A1:N227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11673,6 +11673,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -11759,6 +11759,16 @@
           <t>NODE_S2019_20_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -11768,6 +11778,14 @@
         <is>
           <t>NODE_S2018_19_0002</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -11843,6 +11861,16 @@
           <t>NODE_S2019_20_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
@@ -11852,6 +11880,14 @@
         <is>
           <t>NODE_S2018_19_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -11885,6 +11921,12 @@
           <t>NODE_S2019_20_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -11894,6 +11936,14 @@
         <is>
           <t>NODE_S2018_19_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -11927,6 +11977,16 @@
           <t>NODE_S2019_20_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -11936,6 +11996,14 @@
         <is>
           <t>NODE_S2018_19_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -11969,6 +12037,8 @@
           <t>NODE_S2019_20_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -11978,6 +12048,14 @@
         <is>
           <t>NODE_S2018_19_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -12011,6 +12089,8 @@
           <t>NODE_S2019_20_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12020,6 +12100,14 @@
         <is>
           <t>NODE_S2018_19_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -12053,6 +12141,8 @@
           <t>NODE_S2019_20_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12062,6 +12152,14 @@
         <is>
           <t>NODE_S2018_19_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -12179,6 +12277,16 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12188,6 +12296,14 @@
         <is>
           <t>NODE_S2018_19_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>32 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -12221,6 +12337,16 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12230,6 +12356,14 @@
         <is>
           <t>NODE_S2018_19_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -12263,6 +12397,12 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12272,6 +12412,14 @@
         <is>
           <t>NODE_S2018_19_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -12305,6 +12453,12 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12314,6 +12468,14 @@
         <is>
           <t>NODE_S2018_19_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -12347,6 +12509,8 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12356,6 +12520,14 @@
         <is>
           <t>NODE_S2018_19_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -12389,6 +12561,8 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12398,6 +12572,14 @@
         <is>
           <t>NODE_S2018_19_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -12683,6 +12865,12 @@
           <t>NODE_S2019_20_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12692,6 +12880,14 @@
         <is>
           <t>NODE_S2018_19_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -12725,6 +12921,12 @@
           <t>NODE_S2019_20_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12734,6 +12936,14 @@
         <is>
           <t>NODE_S2018_19_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -12767,6 +12977,12 @@
           <t>NODE_S2019_20_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12776,6 +12992,14 @@
         <is>
           <t>NODE_S2018_19_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -12809,6 +13033,8 @@
           <t>NODE_S2019_20_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12818,6 +13044,14 @@
         <is>
           <t>NODE_S2018_19_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -12851,6 +13085,8 @@
           <t>NODE_S2019_20_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12860,6 +13096,14 @@
         <is>
           <t>NODE_S2018_19_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -13330,10 +13574,24 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0045</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -13515,10 +13773,24 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0050</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -13700,10 +13972,24 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0053</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -13811,10 +14097,20 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -14191,10 +14487,24 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0050</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -14376,10 +14686,24 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0053</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -14487,10 +14811,20 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -14635,10 +14969,24 @@
           <t>NODE_S2019_20_0073</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0076</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -14672,10 +15020,24 @@
           <t>NODE_S2019_20_0073</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0081</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -14857,10 +15219,24 @@
           <t>NODE_S2019_20_0073</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0084</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -14968,10 +15344,20 @@
           <t>NODE_S2019_20_0073</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -15111,10 +15497,24 @@
           <t>NODE_S2019_20_0086</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0089</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -15148,10 +15548,24 @@
           <t>NODE_S2019_20_0086</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0094</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -15333,10 +15747,24 @@
           <t>NODE_S2019_20_0086</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0097</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -15444,10 +15872,20 @@
           <t>NODE_S2019_20_0086</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -15745,10 +16183,24 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0106</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -15782,10 +16234,24 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0111</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -15967,10 +16433,28 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0114</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0121</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="113">
@@ -16078,10 +16562,20 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -16189,10 +16683,24 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0106</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -16226,10 +16734,28 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0114</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0121</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="120">
@@ -16337,10 +16863,20 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -16411,10 +16947,20 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -16670,10 +17216,24 @@
           <t>NODE_S2019_20_0128</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0131</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -16707,10 +17267,24 @@
           <t>NODE_S2019_20_0128</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0134</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -16818,10 +17392,20 @@
           <t>NODE_S2019_20_0128</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -17003,10 +17587,24 @@
           <t>NODE_S2019_20_0137</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0141</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -17077,10 +17675,28 @@
           <t>NODE_S2019_20_0137</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0146</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0144</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="143">
@@ -17188,10 +17804,20 @@
           <t>NODE_S2019_20_0137</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -17262,10 +17888,20 @@
           <t>NODE_S2019_20_0137</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="148">
@@ -17410,10 +18046,24 @@
           <t>NODE_S2019_20_0148</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0151</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -17447,10 +18097,24 @@
           <t>NODE_S2019_20_0148</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0156</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -17632,10 +18296,24 @@
           <t>NODE_S2019_20_0148</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0159</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -17743,10 +18421,20 @@
           <t>NODE_S2019_20_0148</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="161">
@@ -17891,10 +18579,24 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0173</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -17970,10 +18672,28 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0170</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0168</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="167">
@@ -18081,10 +18801,20 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="170">
@@ -18155,10 +18885,20 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="172">
@@ -18266,10 +19006,24 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0165</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -18451,10 +19205,28 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0170</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0168</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="180">
@@ -18562,10 +19334,20 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="183">
@@ -18636,10 +19418,20 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="185">
@@ -18858,10 +19650,24 @@
           <t>NODE_S2019_20_0186</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0190</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -18895,10 +19701,28 @@
           <t>NODE_S2019_20_0186</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0195</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0193</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="192">
@@ -19006,10 +19830,20 @@
           <t>NODE_S2019_20_0186</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="195">
@@ -19080,10 +19914,20 @@
           <t>NODE_S2019_20_0186</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="197">
@@ -19302,10 +20146,24 @@
           <t>NODE_S2019_20_0199</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0202</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -19339,10 +20197,24 @@
           <t>NODE_S2019_20_0199</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0207</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -19524,10 +20396,28 @@
           <t>NODE_S2019_20_0199</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0212</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0210</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="209">
@@ -19635,10 +20525,20 @@
           <t>NODE_S2019_20_0199</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="212">
@@ -19709,10 +20609,20 @@
           <t>NODE_S2019_20_0199</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="214">
@@ -19857,10 +20767,24 @@
           <t>NODE_S2019_20_0214</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0217</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -19894,10 +20818,24 @@
           <t>NODE_S2019_20_0214</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0222</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -20079,10 +21017,24 @@
           <t>NODE_S2019_20_0214</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0225</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="224">
@@ -20190,10 +21142,20 @@
           <t>NODE_S2019_20_0214</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="227">

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -10923,7 +10923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11517,6 +11517,13 @@
       <c r="D27" t="inlineStr">
         <is>
           <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2019/20: play-off zrušeno kvůli COVID-19, titul NEUDĚLEN. Liberec byl 1. po základní části, ale mistr není. Proto bez M badge.</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11933,6 @@
           <t>NODE_S2019_20_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12037,8 +12043,6 @@
           <t>NODE_S2019_20_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12089,8 +12093,6 @@
           <t>NODE_S2019_20_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12141,8 +12143,6 @@
           <t>NODE_S2019_20_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12402,7 +12402,6 @@
           <t>NODE_S2019_20_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12458,7 +12457,6 @@
           <t>NODE_S2019_20_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12509,8 +12507,6 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12561,8 +12557,6 @@
           <t>NODE_S2019_20_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12870,7 +12864,6 @@
           <t>NODE_S2019_20_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12926,7 +12919,6 @@
           <t>NODE_S2019_20_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -12982,7 +12974,6 @@
           <t>NODE_S2019_20_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13033,8 +13024,6 @@
           <t>NODE_S2019_20_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13085,8 +13074,6 @@
           <t>NODE_S2019_20_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13579,7 +13566,6 @@
           <t>NODE_S2019_20_0045</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13778,7 +13764,6 @@
           <t>NODE_S2019_20_0050</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
@@ -13977,7 +13962,6 @@
           <t>NODE_S2019_20_0053</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14097,8 +14081,6 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14492,7 +14474,6 @@
           <t>NODE_S2019_20_0050</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14691,7 +14672,6 @@
           <t>NODE_S2019_20_0053</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14811,8 +14791,6 @@
           <t>NODE_S2019_20_0036</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14974,7 +14952,6 @@
           <t>NODE_S2019_20_0076</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15025,7 +15002,6 @@
           <t>NODE_S2019_20_0081</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15224,7 +15200,6 @@
           <t>NODE_S2019_20_0084</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15344,8 +15319,6 @@
           <t>NODE_S2019_20_0073</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15502,7 +15475,6 @@
           <t>NODE_S2019_20_0089</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15553,7 +15525,6 @@
           <t>NODE_S2019_20_0094</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15752,7 +15723,6 @@
           <t>NODE_S2019_20_0097</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15872,8 +15842,6 @@
           <t>NODE_S2019_20_0086</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16188,7 +16156,6 @@
           <t>NODE_S2019_20_0106</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16239,7 +16206,6 @@
           <t>NODE_S2019_20_0111</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16562,8 +16528,6 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16688,7 +16652,6 @@
           <t>NODE_S2019_20_0106</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16863,8 +16826,6 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16947,8 +16908,6 @@
           <t>NODE_S2019_20_0103</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17221,7 +17180,6 @@
           <t>NODE_S2019_20_0131</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17272,7 +17230,6 @@
           <t>NODE_S2019_20_0134</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17392,8 +17349,6 @@
           <t>NODE_S2019_20_0128</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17592,7 +17547,6 @@
           <t>NODE_S2019_20_0141</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17804,8 +17758,6 @@
           <t>NODE_S2019_20_0137</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17888,8 +17840,6 @@
           <t>NODE_S2019_20_0137</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18051,7 +18001,6 @@
           <t>NODE_S2019_20_0151</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18102,7 +18051,6 @@
           <t>NODE_S2019_20_0156</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18301,7 +18249,6 @@
           <t>NODE_S2019_20_0159</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18421,8 +18368,6 @@
           <t>NODE_S2019_20_0148</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18584,7 +18529,6 @@
           <t>NODE_S2019_20_0173</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18801,8 +18745,6 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18885,8 +18827,6 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19011,7 +18951,6 @@
           <t>NODE_S2019_20_0165</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19334,8 +19273,6 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19418,8 +19355,6 @@
           <t>NODE_S2019_20_0161</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19655,7 +19590,6 @@
           <t>NODE_S2019_20_0190</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19830,8 +19764,6 @@
           <t>NODE_S2019_20_0186</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19914,8 +19846,6 @@
           <t>NODE_S2019_20_0186</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20151,7 +20081,6 @@
           <t>NODE_S2019_20_0202</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20202,7 +20131,6 @@
           <t>NODE_S2019_20_0207</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20525,8 +20453,6 @@
           <t>NODE_S2019_20_0199</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20609,8 +20535,6 @@
           <t>NODE_S2019_20_0199</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20772,7 +20696,6 @@
           <t>NODE_S2019_20_0217</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20823,7 +20746,6 @@
           <t>NODE_S2019_20_0222</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21022,7 +20944,6 @@
           <t>NODE_S2019_20_0225</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21142,8 +21063,6 @@
           <t>NODE_S2019_20_0214</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>complete</t>
@@ -36386,7 +36305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36458,6 +36377,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>2 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(bez titulu — COVID-19)</t>
         </is>
       </c>
     </row>

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -11506,24 +11506,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NODE_S2019_20_0031</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+          <t>2019/20: play-off zrušeno kvůli COVID-19, titul NEUDĚLEN. Liberec byl 1. po základní části, ale mistr není. Proto bez M badge.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2019/20: play-off zrušeno kvůli COVID-19, titul NEUDĚLEN. Liberec byl 1. po základní části, ale mistr není. Proto bez M badge.</t>
+          <t>NODE_S2019_20_0031</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -2640,7 +2640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4122,6 +4122,118 @@
       <c r="U23" s="2" t="n"/>
       <c r="V23" s="2" t="n"/>
       <c r="W23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0228</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Stavební stroje Jičín</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0228</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0251</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00251</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0228</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0252</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00252</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5374,7 +5486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6956,6 +7068,820 @@
       <c r="V30" s="2" t="n"/>
       <c r="W30" s="2" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0229</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0229</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0253</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00253</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0229</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0254</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00254</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ZH Pardubice</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0255</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00255</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HC Orli Chrudim</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0256</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00256</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HC Holomci Jezbořice</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0257</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00257</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AHC Čankovice</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0258</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00258</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HC Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0259</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00259</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HC Sokol Česká Bělá</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0260</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00260</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HC SDH Kostelec u Heřmanova Městce</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0261</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00261</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HC Amat Pardubice</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0262</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00262</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HC Road Cafe Pardubice</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0263</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00263</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>IHC Rebels Polička</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0264</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0265</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HC Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0266</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0267</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HC Čestice</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0268</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Chrudim</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0269</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00269</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6967,7 +7893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7947,6 +8873,407 @@
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n"/>
       <c r="W16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0231</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>soutěž se nekonala</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0231</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0270</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Spartak Polička</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0231</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0271</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0231</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0272</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0232</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0232</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0273</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0232</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0274</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0232</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0275</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0232</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0276</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0232</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0277</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00277</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11618,7 +12945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N227"/>
+  <dimension ref="A1:N233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21111,6 +22438,228 @@
       <c r="J227" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>REG_PHA</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0034</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>REG_LBK</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0137</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0161</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Pardubický – Chrudim</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0161</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0186</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Vysočina – Jihlava</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0186</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -24503,7 +26052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J250"/>
+  <dimension ref="A1:J278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -36291,6 +37840,767 @@
       <c r="J250" t="inlineStr">
         <is>
           <t>Rožnov pod Radhoštěm</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HC Berounští Medvědi</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>HC Berounští Medvědi</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HC Stavební stroje Jičín</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>HC Stavební stroje Jičín</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ZH Pardubice</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>ZH Pardubice</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HC Orli Chrudim</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HC Orli Chrudim</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HC Holomci Jezbořice</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>HC Holomci Jezbořice</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>AHC Čankovice</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>AHC Čankovice</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HC Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>HC Jiskra Skuteč</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HC Sokol Česká Bělá</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>HC Sokol Česká Bělá</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HC SDH Kostelec u Heřmanova Městce</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>HC SDH Kostelec u Heřmanova Městce</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HC Amat Pardubice</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>HC Amat Pardubice</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HC Road Cafe Pardubice</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>HC Road Cafe Pardubice</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>IHC Rebels Polička</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>IHC Rebels Polička</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>HC Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>HC Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>HC Čestice</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>HC Čestice</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>soutěž se nekonala</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>soutěž se nekonala</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Spartak Polička</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Spartak Polička</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>
@@ -39438,7 +41748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -40142,6 +42452,73 @@
       <c r="V9" t="inlineStr">
         <is>
           <t>TR_S2019_20_00079</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0227</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HC Berounští Medvědi</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0227</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S2019_20_0250</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S2019_20_00250</t>
         </is>
       </c>
     </row>

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +116,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -38713,7 +38724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -38770,11 +38781,89 @@
           <t>NODE_S2019_20_0031</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor (Praha) · NODE_S2019_20_0227</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Berounští Medvědi), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2019_20_0228</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Stavební stroje Jičín, HC TS Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga (Pardubický kraj) · NODE_S2019_20_0229</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Světlá nad Sázavou, HC Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12261,7 +12264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12860,6 +12863,57 @@
         </is>
       </c>
       <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0227</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Berounští Medvědi), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0228</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Stavební stroje Jičín, HC TS Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NODE_S2019_20_0229</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Světlá nad Sázavou, HC Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -38801,7 +38855,7 @@
           <t>Praha – Pražský přebor (Praha) · NODE_S2019_20_0227</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Berounští Medvědi), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -38827,7 +38881,7 @@
           <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2019_20_0228</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Stavební stroje Jičín, HC TS Varnsdorf), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -38853,7 +38907,7 @@
           <t>Pardubický – Krajská liga (Pardubický kraj) · NODE_S2019_20_0229</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Světlá nad Sázavou, HC Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -14693,7 +14693,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HK Čáslav – HC Lev Benešov  6:2,6:1</t>
+          <t>HK Čáslav – HC Lev Benešov 6:2,6:1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HK Kralupy nad Vltavou  - SC Kolín "B"  5:3,4:3 SN</t>
+          <t>HK Kralupy nad Vltavou - SC Kolín "B" 5:3,4:3 SN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Slavoj Velké Popovice – HK Lev Slaný  5:3,3:4 PP,6:3</t>
+          <t>Slavoj Velké Popovice – HK Lev Slaný 5:3,3:4 PP,6:3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK Černošice – Slavoj Velké Popovice  5:6 PP,3:4 SN</t>
+          <t>SK Černošice – Slavoj Velké Popovice 5:6 PP,3:4 SN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HC Poděbrady – HC Junior Mělník  5:4,3:7,5:8</t>
+          <t>HC Poděbrady – HC Junior Mělník 5:4,3:7,5:8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BK Mladá Boleslav "B" – HK Kralupy nad Vltavou  6:7 PP,8:4,2:3 SN</t>
+          <t>BK Mladá Boleslav "B" – HK Kralupy nad Vltavou 6:7 PP,8:4,2:3 SN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HK Čáslav – HC Rakovník  2:3,3:2,4:5 PP</t>
+          <t>HK Čáslav – HC Rakovník 2:3,3:2,4:5 PP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HC Rakovník – Slavoj Velké Popovice  2:3 PP, zrušeno</t>
+          <t>HC Rakovník – Slavoj Velké Popovice 2:3 PP, zrušeno</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HK Kralupy nad Vltavou  - HC Junior Mělník zrušeno</t>
+          <t>HK Kralupy nad Vltavou - HC Junior Mělník zrušeno</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HC Příbram "B" – HC Žabonosy   12:2,5:3</t>
+          <t>HC Příbram "B" – HC Žabonosy 12:2,5:3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HC Žabonosy – HC Buldoci Neratovice  zrušeno (Žabonosy se udržely v KLM)</t>
+          <t>HC Žabonosy – HC Buldoci Neratovice zrušeno (Žabonosy se udržely v KLM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HC Benátky nad Jizerou  "B" – HC Buldoci Neratovice 4:8, 2:6</t>
+          <t>HC Benátky nad Jizerou "B" – HC Buldoci Neratovice 4:8, 2:6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HC Pelhřimov – HC Milevsko 2010   8:7,7:1</t>
+          <t>HC Pelhřimov – HC Milevsko 2010 8:7,7:1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov – HC Strakonice  2:5,4:5 PP</t>
+          <t>Slavoj Český Krumlov – HC Strakonice 2:5,4:5 PP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jiskra Humpolec – OLH Spartak Soběslav  2:1 PP,3:9,3:7</t>
+          <t>Jiskra Humpolec – OLH Spartak Soběslav 2:1 PP,3:9,3:7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HC Pelhřimov – HC Strakonice   7:3,7:6 PP</t>
+          <t>HC Pelhřimov – HC Strakonice 7:3,7:6 PP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TJ Sokol Radomyšl – OLH Spartak Soběslav  4:5,3:8</t>
+          <t>TJ Sokol Radomyšl – OLH Spartak Soběslav 4:5,3:8</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HC Pelhřimov – OLH Spartak Soběslav  zrušeno</t>
+          <t>HC Pelhřimov – OLH Spartak Soběslav zrušeno</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HC Buldoci Stříbro – HC Saxana Group  1:5*, 3:1, nájezdy 0:1</t>
+          <t>HC Buldoci Stříbro – HC Saxana Group 1:5*, 3:1, nájezdy 0:1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -17137,7 +17137,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HC Chotíkov "A" – HC Saxana  Group  zrušeno</t>
+          <t>HC Chotíkov "A" – HC Saxana Group zrušeno</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HC Rokycany – Sokol Malá Víska  zrušeno</t>
+          <t>HC Rokycany – Sokol Malá Víska zrušeno</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30_Plzeňský-KV L40</t>
+          <t>Plzeňský-KV, 4. úroveň</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Stadion Cheb – HC Klatovy "B"  zrušeno</t>
+          <t>Stadion Cheb – HC Klatovy "B" zrušeno</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HC Auta &amp; Auta Cheb  - SK HC MAAN Cheb  2:1 PP,5:0</t>
+          <t>HC Auta &amp; Auta Cheb - SK HC MAAN Cheb 2:1 PP,5:0</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Stadion Cheb  "B" – IHT Brimstones Cheb  2:6,3:6</t>
+          <t>Stadion Cheb "B" – IHT Brimstones Cheb 2:6,3:6</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SK HC MAAN Cheb - Stadion Cheb "B"  zrušeno</t>
+          <t>SK HC MAAN Cheb - Stadion Cheb "B" zrušeno</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HC Auta &amp; Auta Cheb  - IHT Brimstones Cheb zrušeno</t>
+          <t>HC Auta &amp; Auta Cheb - IHT Brimstones Cheb zrušeno</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HC Slovan Louny – SK Kadaň "B"  13:4,6:5 SN</t>
+          <t>HC Slovan Louny – SK Kadaň "B" 13:4,6:5 SN</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HC Tygři Klášterec nad Ohří  - HC Roudnice nad Labem  10:2,2:5,6:4</t>
+          <t>HC Tygři Klášterec nad Ohří - HC Roudnice nad Labem 10:2,2:5,6:4</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HC Slovan Louny – HC Tygři Klášterec nad Ohří  4:6,8:7 SN,5:6</t>
+          <t>HC Slovan Louny – HC Tygři Klášterec nad Ohří 4:6,8:7 SN,5:6</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -19053,7 +19053,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HC Stavební stroje Jičín – HC Turnov 1931  4:1,5:1,2:5,1:4,6:3</t>
+          <t>HC Stavební stroje Jičín – HC Turnov 1931 4:1,5:1,2:5,1:4,6:3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HC Frýdlant – HC Lomnice nad Popelkou  3:1,5:2,9:6</t>
+          <t>HC Frýdlant – HC Lomnice nad Popelkou 3:1,5:2,9:6</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HC Lomnice nad Popelkou  - HC Turnov 1931  zrušeno</t>
+          <t>HC Lomnice nad Popelkou - HC Turnov 1931 zrušeno</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HC Stavební stroje Jičín – HC Frýdlant  zrušeno</t>
+          <t>HC Stavební stroje Jičín – HC Frýdlant zrušeno</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – TJ Spartak Nové Město nad Metují  14:2,7:2</t>
+          <t>Stadion Nový Bydžov – TJ Spartak Nové Město nad Metují 14:2,7:2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HC Wikov Hronov – HC Baroni Opočno  2:1 SN,3:2</t>
+          <t>HC Wikov Hronov – HC Baroni Opočno 2:1 SN,3:2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HC Náchod – HC Trutnov "B"  5:1,5:2</t>
+          <t>HC Náchod – HC Trutnov "B" 5:1,5:2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HC Jaroměř – SK Třebechovice pod Orebem  0:5 K,2:9</t>
+          <t>HC Jaroměř – SK Třebechovice pod Orebem 0:5 K,2:9</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – SK Třebechovice pod Orebem  7:2,3:4,6:1,4:0</t>
+          <t>Stadion Nový Bydžov – SK Třebechovice pod Orebem 7:2,3:4,6:1,4:0</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HC Wikov Hronov – HC Náchod  4:1,3:4 PP,2:4,5:2,5:6</t>
+          <t>HC Wikov Hronov – HC Náchod 4:1,3:4 PP,2:4,5:2,5:6</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – HC Náchod  zrušeno</t>
+          <t>Stadion Nový Bydžov – HC Náchod zrušeno</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HC Kohouti Česká Třebová – HC Litomyšl  4:0,5:1,12:3</t>
+          <t>HC Kohouti Česká Třebová – HC Litomyšl 4:0,5:1,12:3</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HC Hlinsko – HC Světlá nad Sázavou  5:4 PP,3:4,2:5,2:3</t>
+          <t>HC Hlinsko – HC Světlá nad Sázavou 5:4 PP,3:4,2:5,2:3</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HC Kohouti Česká Třebová – HC Světlá nad Sázavou  2:3, zrušeno</t>
+          <t>HC Kohouti Česká Třebová – HC Světlá nad Sázavou 2:3, zrušeno</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -20365,7 +20365,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HC Kohouti Česká Třebová – HC Chotěboř  5:2,2:5,3:4,2:3 SN</t>
+          <t>HC Kohouti Česká Třebová – HC Chotěboř 5:2,2:5,3:4,2:3 SN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – HC Litomyšl  6:7,6:1,6:3,9:6</t>
+          <t>Slovan Moravská Třebová – HC Litomyšl 6:7,6:1,6:3,9:6</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HC Spartak Choceň – HC Světlá nad Sázavou  4:3,4:2,3:2 PP</t>
+          <t>HC Spartak Choceň – HC Světlá nad Sázavou 4:3,4:2,3:2 PP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -20476,7 +20476,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HC Chrudim – HC Hlinsko  7:0,3:1,5:4</t>
+          <t>HC Chrudim – HC Hlinsko 7:0,3:1,5:4</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -20568,7 +20568,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová – HC Chotěboř  4:3 PP,3:4,5:4 SN,4:6,5:3</t>
+          <t>Slovan Moravská Třebová – HC Chotěboř 4:3 PP,3:4,5:4 SN,4:6,5:3</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -20605,7 +20605,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HC Spartak Choceň – HC Chrudim  1:2 SN,2:1 SN,3:2 SN,3:6,1:4</t>
+          <t>HC Spartak Choceň – HC Chrudim 1:2 SN,2:1 SN,3:2 SN,3:6,1:4</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HC Zastávka – Spartak Polička  zrušeno</t>
+          <t>HC Zastávka – Spartak Polička zrušeno</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -21371,7 +21371,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -21545,7 +21545,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – HC Lvi Břeclav  6:4,4:1</t>
+          <t>HHK Velké Meziříčí – HC Lvi Břeclav 6:4,4:1</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SKMB Boskovice – HK Kroměříž  5:4 PP,8:5</t>
+          <t>SKMB Boskovice – HK Kroměříž 5:4 PP,8:5</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hokej Uherský Ostroh – Spartak Uherský Brod  8:0,6:3</t>
+          <t>Hokej Uherský Ostroh – Spartak Uherský Brod 8:0,6:3</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -21656,7 +21656,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HC Uničov - SHKM Hodonín  4:5 PP,4:5 PP</t>
+          <t>HC Uničov - SHKM Hodonín 4:5 PP,4:5 PP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – SHKM Hodonín  2:1,2:3 SN,5:2</t>
+          <t>HHK Velké Meziříčí – SHKM Hodonín 2:1,2:3 SN,5:2</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SKMB Boskovice – Hokej Uherský Ostroh   5:3,5:4 PP</t>
+          <t>SKMB Boskovice – Hokej Uherský Ostroh 5:3,5:4 PP</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -21949,7 +21949,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – SKMB Boskovice  zrušeno</t>
+          <t>HHK Velké Meziříčí – SKMB Boskovice zrušeno</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -21986,7 +21986,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HC Studénka – HC Orli Orlová 1930  3:1,1:3,5:2</t>
+          <t>HC Studénka – HC Orli Orlová 1930 3:1,1:3,5:2</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Ďáblové Nový Jičín "B" – HC Wolves Český Těšín  4:5 PP,2:5</t>
+          <t>Ďáblové Nový Jičín "B" – HC Wolves Český Těšín 4:5 PP,2:5</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -22234,7 +22234,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HC Bospor Bohumín – HC Býci Karviná  5:0,1:4,4:3</t>
+          <t>HC Bospor Bohumín – HC Býci Karviná 5:0,1:4,4:3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HC Frýdek-Místek "B" – HK Krnov  1:3,5:1,3:2 SN</t>
+          <t>HC Frýdek-Místek "B" – HK Krnov 1:3,5:1,3:2 SN</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HC Studénka – HC Wolves Český Těšín  1:5,3:6</t>
+          <t>HC Studénka – HC Wolves Český Těšín 1:5,3:6</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>HC Bospor Bohumín – HC Frýdek-Místek "B"  3:4,3:7</t>
+          <t>HC Bospor Bohumín – HC Frýdek-Místek "B" 3:4,3:7</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -22477,7 +22477,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HC Frýdek-Místek "B" – HC Wolves Český Těšín   zrušeno</t>
+          <t>HC Frýdek-Místek "B" – HC Wolves Český Těšín zrušeno</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">

--- a/data/S2019_20_FINAL.xlsx
+++ b/data/S2019_20_FINAL.xlsx
@@ -2945,7 +2945,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -51992,7 +51992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -52065,7 +52065,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -52211,7 +52211,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -52284,7 +52284,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -52357,7 +52357,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -52430,7 +52430,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -52503,7 +52503,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -52576,7 +52576,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -52649,7 +52649,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -52722,7 +52722,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
